--- a/exports/BDL_full_report.xlsx
+++ b/exports/BDL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>4.46</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44602.38541666666</v>
+        <v>44602.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>233.1</v>
+        <v>232.5</v>
       </c>
       <c r="I2" t="n">
         <v>232.9198448791648</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>16.84</v>
+        <v>16.54</v>
       </c>
       <c r="L2" t="n">
         <v>0.2</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>8.99</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44620.55208333334</v>
+        <v>44622.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>225.55</v>
+        <v>235.5</v>
       </c>
       <c r="I3" t="n">
         <v>226.4641666412608</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>18</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>2.99</v>
+        <v>-1.29</v>
       </c>
       <c r="L3" t="n">
         <v>4</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>11.59</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44678.55208333334</v>
+        <v>44679.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>380.35</v>
+        <v>370.9</v>
       </c>
       <c r="I4" t="n">
         <v>373.0921643336274</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>57</v>
       </c>
       <c r="K4" t="n">
-        <v>61.51</v>
+        <v>57.49</v>
       </c>
       <c r="L4" t="n">
         <v>6.84</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>15.81</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44698.38541666666</v>
+        <v>44698.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="I5" t="n">
         <v>355.7244062146129</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>4.29</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
         <v>6.09</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>13.76</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44729.55208333334</v>
+        <v>44732.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>407.25</v>
+        <v>364.9</v>
       </c>
       <c r="I6" t="n">
         <v>373.7531214036138</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>31</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K6" t="n">
-        <v>14.08</v>
+        <v>2.21</v>
       </c>
       <c r="L6" t="n">
         <v>4.65</v>
@@ -783,7 +854,7 @@
         <v>2.87</v>
       </c>
       <c r="N6" t="n">
-        <v>5.43</v>
+        <v>12.22</v>
       </c>
       <c r="O6" t="n">
         <v>3.18</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>20.58</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44762.55208333334</v>
+        <v>44763.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>359.5</v>
+        <v>363.4</v>
       </c>
       <c r="I7" t="n">
         <v>362.7275383423029</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K7" t="n">
-        <v>1.48</v>
+        <v>0.41</v>
       </c>
       <c r="L7" t="n">
         <v>13.29</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.73</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>417.5</v>
+        <v>401.85</v>
       </c>
       <c r="I8" t="n">
         <v>403.0117496098914</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K8" t="n">
-        <v>14.89</v>
+        <v>10.58</v>
       </c>
       <c r="L8" t="n">
         <v>3.96</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>10.23</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44816.55208333334</v>
+        <v>44817.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>420.5</v>
+        <v>428.65</v>
       </c>
       <c r="I9" t="n">
         <v>427.6134773851658</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.64</v>
+        <v>-6.67</v>
       </c>
       <c r="L9" t="n">
-        <v>6.26</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M9" t="n">
         <v>0.84</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.25</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44830.38541666666</v>
+        <v>44830.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>434.75</v>
+        <v>427.5</v>
       </c>
       <c r="I10" t="n">
         <v>432.1992573189694</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>1.42</v>
+        <v>-0.27</v>
       </c>
       <c r="L10" t="n">
         <v>2.01</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>10.21</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44837.55208333334</v>
+        <v>44838.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>438.5</v>
+        <v>456.15</v>
       </c>
       <c r="I11" t="n">
         <v>452.7630982964504</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.57</v>
+        <v>-6.7</v>
       </c>
       <c r="L11" t="n">
-        <v>3.74</v>
+        <v>7.82</v>
       </c>
       <c r="M11" t="n">
         <v>1.02</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>10.07</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44848.55208333334</v>
+        <v>44851.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>429.5</v>
+        <v>424.5</v>
       </c>
       <c r="I12" t="n">
         <v>424.6652613525482</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.84</v>
+        <v>-6.94</v>
       </c>
       <c r="L12" t="n">
-        <v>6.28</v>
+        <v>8.32</v>
       </c>
       <c r="M12" t="n">
         <v>0.83</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,25 +1316,25 @@
         <v>7.5</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44852.55208333334</v>
+        <v>44853.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>446.45</v>
+        <v>458.3</v>
       </c>
       <c r="I13" t="n">
         <v>456.3419808077299</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.17</v>
+        <v>-7.96</v>
       </c>
       <c r="L13" t="n">
-        <v>6.6</v>
+        <v>11.66</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2</v>
+        <v>0.41</v>
       </c>
       <c r="N13" t="n">
         <v>3.42</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44879.55208333334</v>
+        <v>44880.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>473.25</v>
+        <v>463.6</v>
       </c>
       <c r="I14" t="n">
         <v>464.0652588913197</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K14" t="n">
-        <v>3.26</v>
+        <v>1.16</v>
       </c>
       <c r="L14" t="n">
         <v>2.36</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.35</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44921.38541666666</v>
+        <v>44921.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>440.95</v>
+        <v>455.5</v>
       </c>
       <c r="I15" t="n">
         <v>446.8609031197894</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>41</v>
+        <v>41.16666666666666</v>
       </c>
       <c r="K15" t="n">
-        <v>4.89</v>
+        <v>1.75</v>
       </c>
       <c r="L15" t="n">
         <v>6.99</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>11.9</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>459</v>
+        <v>437.85</v>
       </c>
       <c r="I16" t="n">
         <v>446.6792065831085</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>30</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>0.77</v>
+        <v>-3.87</v>
       </c>
       <c r="L16" t="n">
-        <v>4.22</v>
+        <v>4.37</v>
       </c>
       <c r="M16" t="n">
         <v>0.43</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>8.73</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44972.55208333334</v>
+        <v>44973.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>400.5</v>
+        <v>436.5</v>
       </c>
       <c r="I17" t="n">
         <v>430.1129002546563</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>8.529999999999999</v>
+        <v>0.31</v>
       </c>
       <c r="L17" t="n">
         <v>10.65</v>
@@ -1410,7 +1613,7 @@
         <v>5.08</v>
       </c>
       <c r="N17" t="n">
-        <v>2.15</v>
+        <v>11.99</v>
       </c>
       <c r="O17" t="n">
         <v>1.63</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>12.67</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45071.38541666666</v>
+        <v>45071.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>535.35</v>
+        <v>499</v>
       </c>
       <c r="I18" t="n">
         <v>508.4402057855992</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>98</v>
+        <v>98.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>22.65</v>
+        <v>14.32</v>
       </c>
       <c r="L18" t="n">
         <v>7.79</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>12.45</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45078.55208333334</v>
+        <v>45079.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>554.35</v>
+        <v>560.9</v>
       </c>
       <c r="I19" t="n">
         <v>559.7203326026042</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>-11.09</v>
+        <v>-12.4</v>
       </c>
       <c r="L19" t="n">
-        <v>12.64</v>
+        <v>12.98</v>
       </c>
       <c r="M19" t="n">
         <v>1.42</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>8.19</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45090.55208333334</v>
+        <v>45091.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="I20" t="n">
         <v>552.6710116565371</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.34</v>
+        <v>-1.77</v>
       </c>
       <c r="L20" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="M20" t="n">
         <v>0.06</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45092.55208333334</v>
+        <v>45093.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>564</v>
+        <v>595.35</v>
       </c>
       <c r="I21" t="n">
         <v>587.3374700586045</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.36</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>4.42</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>2.17</v>
+        <v>4.61</v>
       </c>
       <c r="O21" t="n">
         <v>-1.25</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>9.640000000000001</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45099.55208333334</v>
+        <v>45100.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>584.25</v>
+        <v>557.8</v>
       </c>
       <c r="I22" t="n">
         <v>566.2087088897225</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.86</v>
+        <v>-6.31</v>
       </c>
       <c r="L22" t="n">
-        <v>5.03</v>
+        <v>7.08</v>
       </c>
       <c r="M22" t="n">
         <v>0.25</v>
       </c>
       <c r="N22" t="n">
-        <v>2.38</v>
+        <v>5.86</v>
       </c>
       <c r="O22" t="n">
         <v>4.61</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>12.22</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45117.55208333334</v>
+        <v>45118.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>539.1</v>
+        <v>621.4</v>
       </c>
       <c r="I23" t="n">
         <v>572.8619078158492</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K23" t="n">
-        <v>3.35</v>
+        <v>-11.4</v>
       </c>
       <c r="L23" t="n">
-        <v>6.03</v>
+        <v>14.56</v>
       </c>
       <c r="M23" t="n">
         <v>0.75</v>
       </c>
       <c r="N23" t="n">
-        <v>2.14</v>
+        <v>13.99</v>
       </c>
       <c r="O23" t="n">
         <v>-5.86</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>14.45</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45142.38541666666</v>
+        <v>45142.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>589.45</v>
+        <v>581.5</v>
       </c>
       <c r="I24" t="n">
         <v>585.3577485233415</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.14</v>
+        <v>-6.42</v>
       </c>
       <c r="L24" t="n">
         <v>12.78</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>5.13</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45170.55208333334</v>
+        <v>45173.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>572.95</v>
+        <v>594.5</v>
       </c>
       <c r="I25" t="n">
         <v>591.9262525522131</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>28</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>1.47</v>
+        <v>-2.24</v>
       </c>
       <c r="L25" t="n">
-        <v>1.5</v>
+        <v>3.83</v>
       </c>
       <c r="M25" t="n">
         <v>1.2</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>7.31</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45181.38541666666</v>
+        <v>45181.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>561.6</v>
+        <v>542</v>
       </c>
       <c r="I26" t="n">
         <v>560.344791264476</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.53</v>
+        <v>-8.83</v>
       </c>
       <c r="L26" t="n">
-        <v>5.8</v>
+        <v>10.65</v>
       </c>
       <c r="M26" t="n">
         <v>0.03</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.03</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45232.38541666666</v>
+        <v>45232.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>496.05</v>
+        <v>499.8</v>
       </c>
       <c r="I27" t="n">
         <v>497.9041450515924</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>50.83333333333334</v>
+        <v>51</v>
       </c>
       <c r="K27" t="n">
-        <v>8.48</v>
+        <v>7.79</v>
       </c>
       <c r="L27" t="n">
         <v>3.78</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.82</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45314.38541666666</v>
+        <v>45314.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>846.6</v>
+        <v>835</v>
       </c>
       <c r="I28" t="n">
         <v>836.5279858734124</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>81.83333333333333</v>
+        <v>82</v>
       </c>
       <c r="K28" t="n">
-        <v>69.39</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="L28" t="n">
         <v>1.02</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>111</v>
+        <v>112</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45329.55208333334</v>
+        <v>45330.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>876.35</v>
+        <v>933</v>
       </c>
       <c r="I29" t="n">
         <v>902.1955686614714</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.95</v>
+        <v>-11.74</v>
       </c>
       <c r="L29" t="n">
-        <v>9.58</v>
+        <v>13.09</v>
       </c>
       <c r="M29" t="n">
         <v>0.79</v>
       </c>
       <c r="N29" t="n">
-        <v>3.44</v>
+        <v>9.23</v>
       </c>
       <c r="O29" t="n">
         <v>-3.47</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>10.91</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45331.55208333334</v>
+        <v>45334.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>925.5</v>
+        <v>810.15</v>
       </c>
       <c r="I30" t="n">
         <v>855.3408461030814</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.8</v>
+        <v>-13.17</v>
       </c>
       <c r="L30" t="n">
-        <v>6.21</v>
+        <v>13.45</v>
       </c>
       <c r="M30" t="n">
         <v>0.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.32</v>
+        <v>11.94</v>
       </c>
       <c r="O30" t="n">
         <v>9.23</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>22.37</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45345.55208333334</v>
+        <v>45348.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>891.5</v>
+        <v>933.2</v>
       </c>
       <c r="I31" t="n">
         <v>900.9449587980191</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K31" t="n">
-        <v>-10.04</v>
+        <v>-15.19</v>
       </c>
       <c r="L31" t="n">
-        <v>14.97</v>
+        <v>18.43</v>
       </c>
       <c r="M31" t="n">
         <v>1.14</v>
       </c>
       <c r="N31" t="n">
-        <v>3.05</v>
+        <v>6.17</v>
       </c>
       <c r="O31" t="n">
         <v>-11.94</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>11.37</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45362.55208333334</v>
+        <v>45363.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>885</v>
+        <v>859.5</v>
       </c>
       <c r="I32" t="n">
         <v>864.775251669315</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K32" t="n">
-        <v>-5.17</v>
+        <v>-7.9</v>
       </c>
       <c r="L32" t="n">
-        <v>5.59</v>
+        <v>8.43</v>
       </c>
       <c r="M32" t="n">
         <v>0.64</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>11.57</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45394.55208333334</v>
+        <v>45397.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>882.25</v>
+        <v>898.55</v>
       </c>
       <c r="I33" t="n">
         <v>889.1856437934516</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.65</v>
+        <v>-4.54</v>
       </c>
       <c r="L33" t="n">
         <v>5.5</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>9.92</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>953.5</v>
+        <v>921.4</v>
       </c>
       <c r="I34" t="n">
         <v>947.7609182278178</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K34" t="n">
-        <v>6.12</v>
+        <v>2.54</v>
       </c>
       <c r="L34" t="n">
         <v>6.24</v>
@@ -2379,7 +2786,7 @@
         <v>2.12</v>
       </c>
       <c r="N34" t="n">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="O34" t="n">
         <v>0.03</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>10.83</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45427.38541666666</v>
+        <v>45427.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>979.2</v>
+        <v>999</v>
       </c>
       <c r="I35" t="n">
         <v>994.7775762018169</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.27</v>
+        <v>-8.42</v>
       </c>
       <c r="L35" t="n">
-        <v>7.28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M35" t="n">
         <v>0.58</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>9.390000000000001</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45447.55208333334</v>
+        <v>45448.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1436.85</v>
+        <v>1293.2</v>
       </c>
       <c r="I36" t="n">
         <v>1382.444273453001</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K36" t="n">
-        <v>43.83</v>
+        <v>29.45</v>
       </c>
       <c r="L36" t="n">
         <v>2.62</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>4.53</v>
       </c>
       <c r="N36" t="n">
         <v>9.970000000000001</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>22.44</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45457.38541666666</v>
+        <v>45457.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>1529.3</v>
+        <v>1578</v>
       </c>
       <c r="I37" t="n">
         <v>1533.323300218737</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K37" t="n">
-        <v>-18.26</v>
+        <v>-22.02</v>
       </c>
       <c r="L37" t="n">
-        <v>19.54</v>
+        <v>25.06</v>
       </c>
       <c r="M37" t="n">
         <v>2.54</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>11.56</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45489.55208333334</v>
+        <v>45491.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1602</v>
+        <v>1550</v>
       </c>
       <c r="I38" t="n">
         <v>1573.133681199879</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>32</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K38" t="n">
-        <v>1.52</v>
+        <v>-1.77</v>
       </c>
       <c r="L38" t="n">
         <v>5.2</v>
@@ -2607,7 +3062,7 @@
         <v>0.97</v>
       </c>
       <c r="N38" t="n">
-        <v>3.37</v>
+        <v>3.43</v>
       </c>
       <c r="O38" t="n">
         <v>5.43</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>11.16</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45573.55208333334</v>
+        <v>45574.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1147.75</v>
+        <v>1172.15</v>
       </c>
       <c r="I39" t="n">
         <v>1166.666631178085</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>82.16666666666667</v>
+        <v>83</v>
       </c>
       <c r="K39" t="n">
-        <v>25.95</v>
+        <v>24.38</v>
       </c>
       <c r="L39" t="n">
         <v>3.87</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>10.14</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45583.55208333334</v>
+        <v>45586.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1131</v>
+        <v>1116.65</v>
       </c>
       <c r="I40" t="n">
         <v>1128.961452472528</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K40" t="n">
-        <v>-3.51</v>
+        <v>-4.73</v>
       </c>
       <c r="L40" t="n">
-        <v>4.94</v>
+        <v>5.11</v>
       </c>
       <c r="M40" t="n">
         <v>0.25</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45621.55208333334</v>
+        <v>45622.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1000</v>
+        <v>1030</v>
       </c>
       <c r="I41" t="n">
         <v>1029.360852130861</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K41" t="n">
-        <v>10.45</v>
+        <v>7.76</v>
       </c>
       <c r="L41" t="n">
         <v>2.63</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>11.61</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45645.55208333334</v>
+        <v>45646.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1230.5</v>
+        <v>1203.5</v>
       </c>
       <c r="I42" t="n">
         <v>1206.868761786</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>19.47</v>
+        <v>16.84</v>
       </c>
       <c r="L42" t="n">
         <v>3.59</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45673.55208333334</v>
+        <v>45674.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1201.95</v>
+        <v>1272.5</v>
       </c>
       <c r="I43" t="n">
         <v>1225.927897552449</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K43" t="n">
-        <v>0.13</v>
+        <v>-5.73</v>
       </c>
       <c r="L43" t="n">
-        <v>6.02</v>
+        <v>6.23</v>
       </c>
       <c r="M43" t="n">
         <v>0.82</v>
       </c>
       <c r="N43" t="n">
-        <v>6.09</v>
+        <v>6.24</v>
       </c>
       <c r="O43" t="n">
         <v>2.85</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>13.22</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45684.38541666666</v>
+        <v>45684.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="I44" t="n">
         <v>1195.795852385568</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K44" t="n">
-        <v>-5.93</v>
+        <v>-6.09</v>
       </c>
       <c r="L44" t="n">
         <v>7.81</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>11.76</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45722.55208333334</v>
+        <v>45723.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1061.95</v>
+        <v>1137.45</v>
       </c>
       <c r="I45" t="n">
         <v>1071.730397679263</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>38</v>
+        <v>38.83333333333334</v>
       </c>
       <c r="K45" t="n">
-        <v>11.13</v>
+        <v>4.82</v>
       </c>
       <c r="L45" t="n">
         <v>12.55</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>14.23</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>1331.05</v>
+        <v>1226.2</v>
       </c>
       <c r="I46" t="n">
         <v>1235.37273890318</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K46" t="n">
-        <v>17.02</v>
+        <v>7.8</v>
       </c>
       <c r="L46" t="n">
         <v>7.05</v>
       </c>
       <c r="M46" t="n">
-        <v>1.75</v>
+        <v>13.44</v>
       </c>
       <c r="N46" t="n">
-        <v>4.73</v>
+        <v>4.96</v>
       </c>
       <c r="O46" t="n">
         <v>6.5</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>14.74</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45762.38541666666</v>
+        <v>45762.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>1389.4</v>
+        <v>1411</v>
       </c>
       <c r="I47" t="n">
         <v>1406.96831523427</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K47" t="n">
-        <v>-13.31</v>
+        <v>-15.07</v>
       </c>
       <c r="L47" t="n">
-        <v>14.57</v>
+        <v>15.4</v>
       </c>
       <c r="M47" t="n">
         <v>2.56</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>11.99</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45832.55208333334</v>
+        <v>45833.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1853</v>
+        <v>1819.3</v>
       </c>
       <c r="I48" t="n">
         <v>1828.988483745362</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>70</v>
+        <v>70.83333333333333</v>
       </c>
       <c r="K48" t="n">
-        <v>31.33</v>
+        <v>28.94</v>
       </c>
       <c r="L48" t="n">
         <v>2.69</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45835.55208333334</v>
+        <v>45838.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1896.2</v>
+        <v>1946.6</v>
       </c>
       <c r="I49" t="n">
         <v>1946.150643176719</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.23</v>
+        <v>-7</v>
       </c>
       <c r="L49" t="n">
-        <v>4.82</v>
+        <v>7.45</v>
       </c>
       <c r="M49" t="n">
         <v>0.48</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>8.49</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45848.55208333334</v>
+        <v>45849.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1890</v>
+        <v>1873.3</v>
       </c>
       <c r="I50" t="n">
         <v>1882.817533696301</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.91</v>
+        <v>-3.77</v>
       </c>
       <c r="L50" t="n">
-        <v>3.25</v>
+        <v>5.59</v>
       </c>
       <c r="M50" t="n">
         <v>0.51</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>6.15</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45887.38541666666</v>
+        <v>45887.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>1606.1</v>
+        <v>1608.3</v>
       </c>
       <c r="I51" t="n">
         <v>1607.336314718032</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>38</v>
+        <v>38.16666666666666</v>
       </c>
       <c r="K51" t="n">
-        <v>14.26</v>
+        <v>14.15</v>
       </c>
       <c r="L51" t="n">
         <v>1.3</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>7.38</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45894.55208333334</v>
+        <v>45895.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1522.5</v>
+        <v>1488.7</v>
       </c>
       <c r="I52" t="n">
         <v>1489.636196157941</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>-5.33</v>
+        <v>-7.44</v>
       </c>
       <c r="L52" t="n">
-        <v>6.37</v>
+        <v>8.1</v>
       </c>
       <c r="M52" t="n">
-        <v>0.17</v>
+        <v>0.49</v>
       </c>
       <c r="N52" t="n">
         <v>3.64</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.8</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45910.38541666666</v>
+        <v>45910.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>1485.5</v>
+        <v>1502</v>
       </c>
       <c r="I53" t="n">
         <v>1491.020338578197</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K53" t="n">
-        <v>0.21</v>
+        <v>-0.89</v>
       </c>
       <c r="L53" t="n">
         <v>2.22</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.02</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1554</v>
+        <v>1521.6</v>
       </c>
       <c r="I54" t="n">
         <v>1545.544567874969</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K54" t="n">
-        <v>3.46</v>
+        <v>1.3</v>
       </c>
       <c r="L54" t="n">
         <v>2.11</v>
@@ -3519,7 +4166,7 @@
         <v>0.51</v>
       </c>
       <c r="N54" t="n">
-        <v>1.86</v>
+        <v>3.49</v>
       </c>
       <c r="O54" t="n">
         <v>5.26</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>7.53</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45968.55208333334</v>
+        <v>45971.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1446</v>
+        <v>1510.4</v>
       </c>
       <c r="I55" t="n">
         <v>1508.342111713583</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K55" t="n">
-        <v>4.97</v>
+        <v>0.74</v>
       </c>
       <c r="L55" t="n">
         <v>3.75</v>
@@ -3576,7 +4235,7 @@
         <v>2.9</v>
       </c>
       <c r="N55" t="n">
-        <v>3.34</v>
+        <v>4.6</v>
       </c>
       <c r="O55" t="n">
         <v>-3.49</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.93</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45982.38541666666</v>
+        <v>45982.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>1522.9</v>
+        <v>1508.6</v>
       </c>
       <c r="I56" t="n">
         <v>1510.165370875917</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>11</v>
+        <v>11.16666666666667</v>
       </c>
       <c r="K56" t="n">
-        <v>0.83</v>
+        <v>-0.12</v>
       </c>
       <c r="L56" t="n">
         <v>4.02</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>6.13</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46013.38541666666</v>
+        <v>46013.55208333334</v>
       </c>
       <c r="H57" t="n">
-        <v>1400</v>
+        <v>1424.9</v>
       </c>
       <c r="I57" t="n">
         <v>1402.109011220477</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>30.83333333333333</v>
+        <v>31</v>
       </c>
       <c r="K57" t="n">
-        <v>7.2</v>
+        <v>5.55</v>
       </c>
       <c r="L57" t="n">
         <v>3.41</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6.43</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46041.55208333334</v>
+        <v>46042.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1502</v>
+        <v>1464.8</v>
       </c>
       <c r="I58" t="n">
         <v>1465.506198920452</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>28</v>
+        <v>28.83333333333333</v>
       </c>
       <c r="K58" t="n">
-        <v>5.41</v>
+        <v>2.8</v>
       </c>
       <c r="L58" t="n">
         <v>1.81</v>
@@ -3747,7 +4442,7 @@
         <v>0.72</v>
       </c>
       <c r="N58" t="n">
-        <v>0.96</v>
+        <v>3.2</v>
       </c>
       <c r="O58" t="n">
         <v>3.78</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>7.26</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46049.55208333334</v>
+        <v>46050.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1479.4</v>
+        <v>1536.6</v>
       </c>
       <c r="I59" t="n">
         <v>1502.415010572301</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K59" t="n">
-        <v>-1</v>
+        <v>-4.9</v>
       </c>
       <c r="L59" t="n">
-        <v>2.7</v>
+        <v>5.55</v>
       </c>
       <c r="M59" t="n">
         <v>0.37</v>
       </c>
       <c r="N59" t="n">
-        <v>4.77</v>
+        <v>6.46</v>
       </c>
       <c r="O59" t="n">
         <v>-3.2</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>8.960000000000001</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46052.55208333334</v>
+        <v>46054.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1537.5</v>
+        <v>1434.5</v>
       </c>
       <c r="I60" t="n">
         <v>1443.874149907162</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K60" t="n">
-        <v>0.06</v>
+        <v>-6.64</v>
       </c>
       <c r="L60" t="n">
-        <v>4.18</v>
+        <v>9.9</v>
       </c>
       <c r="M60" t="n">
-        <v>0.43</v>
+        <v>2.11</v>
       </c>
       <c r="N60" t="n">
-        <v>2.75</v>
+        <v>10.37</v>
       </c>
       <c r="O60" t="n">
         <v>6.46</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>11.92</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46086.55208333334</v>
+        <v>46087.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1277</v>
+        <v>1346.8</v>
       </c>
       <c r="I61" t="n">
         <v>1314.652113661796</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K61" t="n">
-        <v>10.98</v>
+        <v>6.11</v>
       </c>
       <c r="L61" t="n">
         <v>6.1</v>
@@ -3918,7 +4649,7 @@
         <v>3.29</v>
       </c>
       <c r="N61" t="n">
-        <v>2.98</v>
+        <v>6.11</v>
       </c>
       <c r="O61" t="n">
         <v>-10.37</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>9.699999999999999</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46094.55208333334</v>
+        <v>46097.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>1309.6</v>
+        <v>1265</v>
       </c>
       <c r="I62" t="n">
         <v>1266.8735381852</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.76</v>
+        <v>-6.07</v>
       </c>
       <c r="L62" t="n">
-        <v>5.25</v>
+        <v>6.14</v>
       </c>
       <c r="M62" t="n">
         <v>1.18</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>10.74</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46111.55208333334</v>
+        <v>46113.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1092</v>
+        <v>1205.1</v>
       </c>
       <c r="I63" t="n">
         <v>1203.502829514718</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K63" t="n">
-        <v>13.68</v>
+        <v>4.74</v>
       </c>
       <c r="L63" t="n">
         <v>4.94</v>
       </c>
       <c r="M63" t="n">
-        <v>2.52</v>
+        <v>3.68</v>
       </c>
       <c r="N63" t="n">
-        <v>1.64</v>
+        <v>10.99</v>
       </c>
       <c r="O63" t="n">
         <v>-2.1</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>13.82</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>1403</v>
+        <v>1353.3</v>
       </c>
       <c r="I64" t="n">
         <v>1368.926340274503</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K64" t="n">
-        <v>16.42</v>
+        <v>12.3</v>
       </c>
       <c r="L64" t="n">
         <v>7.05</v>
@@ -4089,7 +4856,7 @@
         <v>3.14</v>
       </c>
       <c r="N64" t="n">
-        <v>3.05</v>
+        <v>4.22</v>
       </c>
       <c r="O64" t="n">
         <v>10.99</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>8.76</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46189.55208333334</v>
+        <v>46190.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>1235</v>
+        <v>1282.2</v>
       </c>
       <c r="I65" t="n">
         <v>1236.86093760549</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K65" t="n">
-        <v>8.74</v>
+        <v>5.25</v>
       </c>
       <c r="L65" t="n">
         <v>3.86</v>
@@ -4146,7 +4925,7 @@
         <v>1.73</v>
       </c>
       <c r="N65" t="n">
-        <v>3.86</v>
+        <v>6.23</v>
       </c>
       <c r="O65" t="n">
         <v>-4.22</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>7.73</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46212.38541666666</v>
+        <v>46212.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>1339.7</v>
+        <v>1325</v>
       </c>
       <c r="I66" t="n">
         <v>1329.380976168363</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>4.48</v>
+        <v>3.34</v>
       </c>
       <c r="L66" t="n">
         <v>3.91</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>6.47</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46239.55208333334</v>
+        <v>46240.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>1237.1</v>
+        <v>1296.1</v>
       </c>
       <c r="I67" t="n">
         <v>1294.491303403583</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K67" t="n">
-        <v>6.63</v>
+        <v>2.18</v>
       </c>
       <c r="L67" t="n">
         <v>2.26</v>
@@ -4260,7 +5063,7 @@
         <v>0.65</v>
       </c>
       <c r="N67" t="n">
-        <v>1.51</v>
+        <v>4.84</v>
       </c>
       <c r="O67" t="n">
         <v>-0.96</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>7.3</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46262.38541666666</v>
+        <v>46262.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>1309.1</v>
+        <v>1307.6</v>
       </c>
       <c r="I68" t="n">
         <v>1308.4351456852</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="L68" t="n">
         <v>4.7</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>6.28</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46308.38541666666</v>
+        <v>46308.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>1113.2</v>
+        <v>1125.9</v>
       </c>
       <c r="I69" t="n">
         <v>1114.868135924162</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>45.83333333333334</v>
+        <v>46</v>
       </c>
       <c r="K69" t="n">
-        <v>14.87</v>
+        <v>13.9</v>
       </c>
       <c r="L69" t="n">
         <v>0.49</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>6.46</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>1085.8</v>
+        <v>1059</v>
       </c>
       <c r="I70" t="n">
         <v>1066.816606088189</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>6</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.56</v>
+        <v>-5.94</v>
       </c>
       <c r="L70" t="n">
-        <v>3.63</v>
+        <v>6.12</v>
       </c>
       <c r="M70" t="n">
         <v>0.8</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,12 @@
       <c r="Q71" t="n">
         <v>10</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7450,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.2</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7460,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21.2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7470,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7480,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7490,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7500,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42.9</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="11">
@@ -6653,7 +7510,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -6663,7 +7520,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13">
@@ -6673,7 +7530,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69.59999999999999</v>
+        <v>63.8</v>
       </c>
     </row>
     <row r="14">
@@ -6683,7 +7540,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.58</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7550,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.77</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7560,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.3</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7570,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>69.39</v>
+        <v>67.06999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7580,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>62.3</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7590,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.52</v>
+        <v>6.68</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7600,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.82</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="21">
@@ -6753,7 +7610,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>19.54</v>
+        <v>25.06</v>
       </c>
     </row>
     <row r="22">
@@ -6763,7 +7620,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
@@ -6773,7 +7630,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -6783,7 +7640,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.35</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="25">
@@ -6793,7 +7650,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.08</v>
+        <v>13.44</v>
       </c>
     </row>
     <row r="26">
@@ -6803,7 +7660,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.21</v>
+        <v>5.46</v>
       </c>
     </row>
     <row r="27">
@@ -6813,7 +7670,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.72</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="28">
@@ -6823,7 +7680,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
